--- a/measurements/35/Filled_2D_sections/coronal/week35_coronal_Batch_Allmarks.xlsx
+++ b/measurements/35/Filled_2D_sections/coronal/week35_coronal_Batch_Allmarks.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:AK32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,12 +487,122 @@
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v2_mm</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v3_mm</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_min_mm</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_max_mm</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_mean_mm</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v3_mm</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_min_mm</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_max_mm</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_mean_mm</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_min_mm</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_max_mm</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>Mean</t>
         </is>
@@ -506,43 +616,76 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7.886674598453302</v>
+        <v>3006.235827664399</v>
       </c>
       <c r="D2" t="n">
-        <v>24.44707499480829</v>
+        <v>477.3000356129238</v>
       </c>
       <c r="E2" t="n">
-        <v>13.40906439757929</v>
+        <v>261.7960191908336</v>
       </c>
       <c r="F2" t="n">
-        <v>1.823175299182072</v>
+        <v>1.823175299182073</v>
       </c>
       <c r="G2" t="n">
         <v>0.1658249888635351</v>
       </c>
       <c r="H2" t="n">
+        <v>11</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.291666666666667</v>
+      </c>
+      <c r="J2" t="n">
+        <v>22.31212797619047</v>
+      </c>
+      <c r="K2" t="n">
+        <v>10.34615124458875</v>
+      </c>
+      <c r="L2" t="n">
         <v>4</v>
       </c>
-      <c r="I2" t="n">
-        <v>0.7073170731707318</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1.14281631097561</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0.8981278582317074</v>
-      </c>
-      <c r="N2" t="inlineStr">
+      <c r="P2" t="n">
+        <v>13.80952380952381</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>22.31212797619047</v>
+      </c>
+      <c r="R2" t="n">
+        <v>17.53487723214286</v>
+      </c>
+      <c r="S2" t="n">
+        <v>6</v>
+      </c>
+      <c r="W2" t="n">
+        <v>4.596354166666666</v>
+      </c>
+      <c r="X2" t="n">
+        <v>9.691220238095237</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>6.896081349206349</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.291666666666667</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
         <is>
           <t>area</t>
         </is>
       </c>
-      <c r="O2" s="2" t="n">
-        <v>8.189143367043426</v>
+      <c r="AK2" s="2" t="n">
+        <v>3121.530612244897</v>
       </c>
     </row>
     <row r="3">
@@ -553,43 +696,82 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8.259666864961332</v>
+        <v>3148.412698412698</v>
       </c>
       <c r="D3" t="n">
-        <v>23.35513473138577</v>
+        <v>455.981201898484</v>
       </c>
       <c r="E3" t="n">
-        <v>13.34007837423464</v>
+        <v>260.4491492112477</v>
       </c>
       <c r="F3" t="n">
-        <v>1.750749439110827</v>
+        <v>1.750749439110826</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1902863524939769</v>
+        <v>0.190286352493977</v>
       </c>
       <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.5234375</v>
+      </c>
+      <c r="J3" t="n">
+        <v>21.63504464285714</v>
+      </c>
+      <c r="K3" t="n">
+        <v>8.727678571428571</v>
+      </c>
+      <c r="L3" t="n">
         <v>4</v>
       </c>
-      <c r="I3" t="n">
-        <v>0.7269435975609756</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1.108136432926829</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.8815739329268293</v>
-      </c>
-      <c r="N3" t="inlineStr">
+      <c r="P3" t="n">
+        <v>14.19270833333333</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>21.63504464285714</v>
+      </c>
+      <c r="R3" t="n">
+        <v>17.21168154761905</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="W3" t="n">
+        <v>4.162946428571428</v>
+      </c>
+      <c r="X3" t="n">
+        <v>7.886904761904762</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>5.821800595238095</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.834821428571428</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>2.418154761904762</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.5234375</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
         <is>
           <t>perimeter</t>
         </is>
       </c>
-      <c r="O3" s="2" t="n">
-        <v>22.15814813404548</v>
+      <c r="AK3" s="2" t="n">
+        <v>432.6114635694595</v>
       </c>
     </row>
     <row r="4">
@@ -600,43 +782,82 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8.375074360499703</v>
+        <v>3192.403628117914</v>
       </c>
       <c r="D4" t="n">
-        <v>23.25757374705338</v>
+        <v>454.0764398234231</v>
       </c>
       <c r="E4" t="n">
-        <v>13.31987283287979</v>
+        <v>260.0546600705101</v>
       </c>
       <c r="F4" t="n">
         <v>1.746080765098794</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1945672417772488</v>
+        <v>0.1945672417772489</v>
       </c>
       <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.191220238095238</v>
+      </c>
+      <c r="J4" t="n">
+        <v>19.86421130952381</v>
+      </c>
+      <c r="K4" t="n">
+        <v>8.557012648809524</v>
+      </c>
+      <c r="L4" t="n">
         <v>4</v>
       </c>
-      <c r="I4" t="n">
-        <v>0.7411394817073171</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1.017435213414634</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0.8614710365853659</v>
-      </c>
-      <c r="N4" t="inlineStr">
+      <c r="P4" t="n">
+        <v>14.46986607142857</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>19.86421130952381</v>
+      </c>
+      <c r="R4" t="n">
+        <v>16.81919642857143</v>
+      </c>
+      <c r="S4" t="n">
+        <v>4</v>
+      </c>
+      <c r="W4" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="X4" t="n">
+        <v>6.934523809523809</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>6.33696056547619</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>2.191220238095238</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>2.767857142857143</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>2.514880952380953</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
         <is>
           <t>perimeter_convex</t>
         </is>
       </c>
-      <c r="O4" s="2" t="n">
-        <v>13.3827551299479</v>
+      <c r="AK4" s="2" t="n">
+        <v>261.2823620608875</v>
       </c>
     </row>
     <row r="5">
@@ -647,17 +868,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8.444378346222488</v>
+        <v>3218.820861678004</v>
       </c>
       <c r="D5" t="n">
-        <v>22.82446742348555</v>
+        <v>445.6205544585273</v>
       </c>
       <c r="E5" t="n">
-        <v>13.38885883587163</v>
+        <v>261.4015296527318</v>
       </c>
       <c r="F5" t="n">
         <v>1.704735833223807</v>
@@ -666,23 +887,62 @@
         <v>0.2036930645137195</v>
       </c>
       <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.133556547619047</v>
+      </c>
+      <c r="J5" t="n">
+        <v>19.6484375</v>
+      </c>
+      <c r="K5" t="n">
+        <v>8.036954365079366</v>
+      </c>
+      <c r="L5" t="n">
         <v>4</v>
       </c>
-      <c r="I5" t="n">
-        <v>0.7422827743902439</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1.006383384146341</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0.8508003048780487</v>
-      </c>
-      <c r="N5" t="inlineStr">
+      <c r="P5" t="n">
+        <v>14.4921875</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>19.6484375</v>
+      </c>
+      <c r="R5" t="n">
+        <v>16.61086309523809</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4</v>
+      </c>
+      <c r="W5" t="n">
+        <v>3.833705357142857</v>
+      </c>
+      <c r="X5" t="n">
+        <v>6.2890625</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>5.103236607142857</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>2.133556547619047</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>2.717633928571428</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>2.396763392857142</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
         <is>
           <t>LGI</t>
         </is>
       </c>
-      <c r="O5" s="2" t="n">
+      <c r="AK5" s="2" t="n">
         <v>1.65576733231908</v>
       </c>
     </row>
@@ -694,17 +954,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>8.477691850089233</v>
+        <v>3231.519274376417</v>
       </c>
       <c r="D6" t="n">
-        <v>22.4864707254782</v>
+        <v>439.0215713069552</v>
       </c>
       <c r="E6" t="n">
-        <v>13.38294075756538</v>
+        <v>261.2859862191336</v>
       </c>
       <c r="F6" t="n">
         <v>1.680233898724134</v>
@@ -713,23 +973,62 @@
         <v>0.210690471491871</v>
       </c>
       <c r="H6" t="n">
+        <v>13</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.489955357142857</v>
+      </c>
+      <c r="J6" t="n">
+        <v>19.71168154761905</v>
+      </c>
+      <c r="K6" t="n">
+        <v>7.26605425824176</v>
+      </c>
+      <c r="L6" t="n">
         <v>4</v>
       </c>
-      <c r="I6" t="n">
-        <v>0.7540015243902439</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1.009622713414634</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.8487995426829269</v>
-      </c>
-      <c r="N6" t="inlineStr">
+      <c r="P6" t="n">
+        <v>14.72098214285714</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>19.71168154761905</v>
+      </c>
+      <c r="R6" t="n">
+        <v>16.57180059523809</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3</v>
+      </c>
+      <c r="T6" t="n">
+        <v>5.5078125</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3.962053571428571</v>
+      </c>
+      <c r="V6" t="n">
+        <v>3.856026785714286</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.489955357142857</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>3.49516369047619</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>2.474268353174603</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
         <is>
           <t>Compactness</t>
         </is>
       </c>
-      <c r="O6" s="2" t="n">
+      <c r="AK6" s="2" t="n">
         <v>0.2116000345760325</v>
       </c>
     </row>
@@ -741,17 +1040,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>8.39767995240928</v>
+        <v>3201.020408163265</v>
       </c>
       <c r="D7" t="n">
-        <v>23.6631204965638</v>
+        <v>461.9942573138645</v>
       </c>
       <c r="E7" t="n">
-        <v>13.28783116398788</v>
+        <v>259.4290846302396</v>
       </c>
       <c r="F7" t="n">
         <v>1.780811345699107</v>
@@ -760,24 +1059,63 @@
         <v>0.1884625888523173</v>
       </c>
       <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.556919642857143</v>
+      </c>
+      <c r="J7" t="n">
+        <v>20.71986607142857</v>
+      </c>
+      <c r="K7" t="n">
+        <v>8.216610863095235</v>
+      </c>
+      <c r="L7" t="n">
+        <v>4</v>
+      </c>
+      <c r="P7" t="n">
+        <v>14.57775297619047</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>20.71986607142857</v>
+      </c>
+      <c r="R7" t="n">
+        <v>16.48856026785714</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="n">
+        <v>10.48363095238095</v>
+      </c>
+      <c r="U7" t="n">
+        <v>5.535714285714286</v>
+      </c>
+      <c r="V7" t="n">
+        <v>3.839285714285714</v>
+      </c>
+      <c r="Z7" t="n">
         <v>5</v>
       </c>
-      <c r="I7" t="n">
-        <v>0.5369664634146342</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1.061261432926829</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.7830221036585365</v>
-      </c>
-      <c r="N7" t="inlineStr">
+      <c r="AD7" t="n">
+        <v>1.556919642857143</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>3.720238095238095</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>2.557291666666667</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
         <is>
           <t>Sulci_count</t>
         </is>
       </c>
-      <c r="O7" s="2" t="n">
-        <v>4.25</v>
+      <c r="AK7" s="2" t="n">
+        <v>11.5</v>
       </c>
     </row>
     <row r="8">
@@ -788,17 +1126,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>8.349791790600833</v>
+        <v>3182.766439909297</v>
       </c>
       <c r="D8" t="n">
-        <v>24.23766556600245</v>
+        <v>473.2115658124288</v>
       </c>
       <c r="E8" t="n">
-        <v>13.38885882133391</v>
+        <v>261.4015293689001</v>
       </c>
       <c r="F8" t="n">
         <v>1.810286140845848</v>
@@ -807,24 +1145,63 @@
         <v>0.1786092441720106</v>
       </c>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I8" t="n">
-        <v>0.551733993902439</v>
+        <v>1.350446428571429</v>
       </c>
       <c r="J8" t="n">
-        <v>1.060403963414634</v>
+        <v>20.703125</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7687118902439025</v>
-      </c>
-      <c r="N8" t="inlineStr">
+        <v>8.520585317460316</v>
+      </c>
+      <c r="L8" t="n">
+        <v>4</v>
+      </c>
+      <c r="P8" t="n">
+        <v>14.19084821428571</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>20.703125</v>
+      </c>
+      <c r="R8" t="n">
+        <v>16.06724330357143</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4</v>
+      </c>
+      <c r="W8" t="n">
+        <v>4.055059523809524</v>
+      </c>
+      <c r="X8" t="n">
+        <v>10.7719494047619</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>7.114490327380953</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.350446428571429</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>3.309151785714286</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>2.380022321428572</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
         <is>
           <t>min_depth_mm</t>
         </is>
       </c>
-      <c r="O8" s="2" t="n">
-        <v>0.6090129573170732</v>
+      <c r="AK8" s="2" t="n">
+        <v>1.801897321428572</v>
       </c>
     </row>
     <row r="9">
@@ -835,43 +1212,82 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>8.324509220701964</v>
+        <v>3173.12925170068</v>
       </c>
       <c r="D9" t="n">
-        <v>23.3349291493253</v>
+        <v>455.5867119630178</v>
       </c>
       <c r="E9" t="n">
-        <v>13.29374921031115</v>
+        <v>259.5446274394081</v>
       </c>
       <c r="F9" t="n">
-        <v>1.755330928856837</v>
+        <v>1.755330928856836</v>
       </c>
       <c r="G9" t="n">
         <v>0.1921124583817887</v>
       </c>
       <c r="H9" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5402057926829269</v>
+        <v>2.204241071428571</v>
       </c>
       <c r="J9" t="n">
-        <v>1.067644817073171</v>
+        <v>20.84449404761905</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7421493902439025</v>
-      </c>
-      <c r="N9" t="inlineStr">
+        <v>9.066727543290042</v>
+      </c>
+      <c r="L9" t="n">
+        <v>4</v>
+      </c>
+      <c r="P9" t="n">
+        <v>12.79389880952381</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>20.84449404761905</v>
+      </c>
+      <c r="R9" t="n">
+        <v>15.47526041666667</v>
+      </c>
+      <c r="S9" t="n">
+        <v>4</v>
+      </c>
+      <c r="W9" t="n">
+        <v>4.53125</v>
+      </c>
+      <c r="X9" t="n">
+        <v>10.546875</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>7.398623511904761</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>3.439360119047619</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.594866071428571</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.204241071428571</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
         <is>
           <t>max_depth_mm</t>
         </is>
       </c>
-      <c r="O9" s="2" t="n">
-        <v>1.062076028963415</v>
+      <c r="AK9" s="2" t="n">
+        <v>20.73577008928572</v>
       </c>
     </row>
     <row r="10">
@@ -882,43 +1298,82 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>8.215348007138608</v>
+        <v>3131.519274376417</v>
       </c>
       <c r="D10" t="n">
-        <v>22.78405631460795</v>
+        <v>444.8315756661551</v>
       </c>
       <c r="E10" t="n">
-        <v>13.6362280176907</v>
+        <v>266.2311184406281</v>
       </c>
       <c r="F10" t="n">
-        <v>1.670847413599236</v>
+        <v>1.670847413599235</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1988720444388172</v>
+        <v>0.1988720444388173</v>
       </c>
       <c r="H10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5465891768292683</v>
+        <v>2.486979166666667</v>
       </c>
       <c r="J10" t="n">
-        <v>1.043349847560976</v>
+        <v>20.37016369047619</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7509146341463415</v>
-      </c>
-      <c r="N10" t="inlineStr">
+        <v>9.75688244047619</v>
+      </c>
+      <c r="L10" t="n">
+        <v>4</v>
+      </c>
+      <c r="P10" t="n">
+        <v>13.74255952380952</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>20.37016369047619</v>
+      </c>
+      <c r="R10" t="n">
+        <v>15.65801711309524</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
+        <v>10.67150297619048</v>
+      </c>
+      <c r="U10" t="n">
+        <v>7.531622023809524</v>
+      </c>
+      <c r="V10" t="n">
+        <v>7.354910714285714</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>3.809523809523809</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>3.082217261904762</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.486979166666667</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
         <is>
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="O10" s="2" t="n">
-        <v>0.8261378144054878</v>
+      <c r="AK10" s="2" t="n">
+        <v>8.330956792773199</v>
       </c>
     </row>
     <row r="11">
@@ -929,17 +1384,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>8.160023795359905</v>
+        <v>3110.430839002267</v>
       </c>
       <c r="D11" t="n">
-        <v>22.51504566611313</v>
+        <v>439.5794630050659</v>
       </c>
       <c r="E11" t="n">
-        <v>13.69929598017437</v>
+        <v>267.4624453272138</v>
       </c>
       <c r="F11" t="n">
         <v>1.643518447860162</v>
@@ -948,16 +1403,63 @@
         <v>0.2022812482334294</v>
       </c>
       <c r="H11" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5307736280487805</v>
+        <v>1.800595238095238</v>
       </c>
       <c r="J11" t="n">
-        <v>1.056497713414634</v>
+        <v>20.62686011904762</v>
       </c>
       <c r="K11" t="n">
-        <v>0.7514672256097561</v>
+        <v>9.187973484848484</v>
+      </c>
+      <c r="L11" t="n">
+        <v>4</v>
+      </c>
+      <c r="P11" t="n">
+        <v>13.34449404761905</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>20.62686011904762</v>
+      </c>
+      <c r="R11" t="n">
+        <v>15.74869791666667</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4</v>
+      </c>
+      <c r="W11" t="n">
+        <v>3.9453125</v>
+      </c>
+      <c r="X11" t="n">
+        <v>10.36272321428571</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>7.432570684523809</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>3.431919642857143</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>3.110119047619047</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.800595238095238</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="AK11" s="2" t="n">
+        <v>3.7</v>
       </c>
     </row>
     <row r="12">
@@ -968,17 +1470,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>8.145449137418204</v>
+        <v>3104.875283446712</v>
       </c>
       <c r="D12" t="n">
-        <v>21.58720102833539</v>
+        <v>421.4644010294051</v>
       </c>
       <c r="E12" t="n">
-        <v>13.59336557620909</v>
+        <v>265.3942802974156</v>
       </c>
       <c r="F12" t="n">
         <v>1.588068893410546</v>
@@ -987,16 +1489,63 @@
         <v>0.2196505163133951</v>
       </c>
       <c r="H12" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="I12" t="n">
-        <v>0.534203506097561</v>
+        <v>1.871279761904762</v>
       </c>
       <c r="J12" t="n">
-        <v>1.092225609756098</v>
+        <v>21.32440476190476</v>
       </c>
       <c r="K12" t="n">
-        <v>0.8166920731707317</v>
+        <v>8.058035714285714</v>
+      </c>
+      <c r="L12" t="n">
+        <v>3</v>
+      </c>
+      <c r="M12" t="n">
+        <v>21.32440476190476</v>
+      </c>
+      <c r="N12" t="n">
+        <v>16.68526785714286</v>
+      </c>
+      <c r="O12" t="n">
+        <v>15.34040178571428</v>
+      </c>
+      <c r="S12" t="n">
+        <v>6</v>
+      </c>
+      <c r="W12" t="n">
+        <v>3.785342261904762</v>
+      </c>
+      <c r="X12" t="n">
+        <v>10.4296875</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>6.146763392857142</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.336309523809524</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.258184523809524</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.871279761904762</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AK12" s="2" t="n">
+        <v>20.79923115079365</v>
       </c>
     </row>
     <row r="13">
@@ -1007,17 +1556,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>8.094289113622844</v>
+        <v>3085.374149659864</v>
       </c>
       <c r="D13" t="n">
-        <v>21.0032711581486</v>
+        <v>410.0638654686156</v>
       </c>
       <c r="E13" t="n">
-        <v>13.36620197354294</v>
+        <v>260.9591813882192</v>
       </c>
       <c r="F13" t="n">
         <v>1.571371673099246</v>
@@ -1026,16 +1575,63 @@
         <v>0.2305763170683587</v>
       </c>
       <c r="H13" t="n">
+        <v>11</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.062872023809524</v>
+      </c>
+      <c r="J13" t="n">
+        <v>20.82217261904762</v>
+      </c>
+      <c r="K13" t="n">
+        <v>8.331473214285712</v>
+      </c>
+      <c r="L13" t="n">
+        <v>3</v>
+      </c>
+      <c r="M13" t="n">
+        <v>20.82217261904762</v>
+      </c>
+      <c r="N13" t="n">
+        <v>16.59412202380952</v>
+      </c>
+      <c r="O13" t="n">
+        <v>15.90587797619047</v>
+      </c>
+      <c r="S13" t="n">
         <v>4</v>
       </c>
-      <c r="I13" t="n">
-        <v>0.5552591463414634</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1.066501524390244</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0.8215987042682927</v>
+      <c r="W13" t="n">
+        <v>4.358258928571428</v>
+      </c>
+      <c r="X13" t="n">
+        <v>10.84077380952381</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>6.980096726190475</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>2.062872023809524</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>3.130580357142857</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.600911458333333</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>Primary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AK13" s="2" t="n">
+        <v>16.73270089285714</v>
       </c>
     </row>
     <row r="14">
@@ -1046,17 +1642,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>8.120166567519334</v>
+        <v>3095.238095238095</v>
       </c>
       <c r="D14" t="n">
-        <v>20.78549233006268</v>
+        <v>405.8119931107476</v>
       </c>
       <c r="E14" t="n">
-        <v>13.35783257135531</v>
+        <v>260.7957787740798</v>
       </c>
       <c r="F14" t="n">
         <v>1.556052766721701</v>
@@ -1065,16 +1661,63 @@
         <v>0.2361860105131012</v>
       </c>
       <c r="H14" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5292492378048781</v>
+        <v>1.489955357142857</v>
       </c>
       <c r="J14" t="n">
-        <v>1.064881859756098</v>
+        <v>20.79055059523809</v>
       </c>
       <c r="K14" t="n">
-        <v>0.8160489710365855</v>
+        <v>7.576109871031746</v>
+      </c>
+      <c r="L14" t="n">
+        <v>3</v>
+      </c>
+      <c r="M14" t="n">
+        <v>20.79055059523809</v>
+      </c>
+      <c r="N14" t="n">
+        <v>16.51785714285714</v>
+      </c>
+      <c r="O14" t="n">
+        <v>16.08816964285714</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3</v>
+      </c>
+      <c r="T14" t="n">
+        <v>10.33296130952381</v>
+      </c>
+      <c r="U14" t="n">
+        <v>7.289806547619047</v>
+      </c>
+      <c r="V14" t="n">
+        <v>4.761904761904762</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.489955357142857</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>3.353794642857143</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>2.522011408730159</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>Primary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AK14" s="2" t="n">
+        <v>16.12816220238095</v>
       </c>
     </row>
     <row r="15">
@@ -1085,35 +1728,82 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>8.159726353361094</v>
+        <v>3110.31746031746</v>
       </c>
       <c r="D15" t="n">
-        <v>20.50363014674768</v>
+        <v>400.3089695317404</v>
       </c>
       <c r="E15" t="n">
-        <v>13.43273663811567</v>
+        <v>262.2581915060679</v>
       </c>
       <c r="F15" t="n">
-        <v>1.526392625652184</v>
+        <v>1.526392625652185</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2439068176911677</v>
+        <v>0.2439068176911678</v>
       </c>
       <c r="H15" t="n">
+        <v>12</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.772693452380952</v>
+      </c>
+      <c r="J15" t="n">
+        <v>20.78125</v>
+      </c>
+      <c r="K15" t="n">
+        <v>7.557973710317458</v>
+      </c>
+      <c r="L15" t="n">
+        <v>3</v>
+      </c>
+      <c r="M15" t="n">
+        <v>20.78125</v>
+      </c>
+      <c r="N15" t="n">
+        <v>16.59598214285714</v>
+      </c>
+      <c r="O15" t="n">
+        <v>16.47135416666666</v>
+      </c>
+      <c r="S15" t="n">
         <v>4</v>
       </c>
-      <c r="I15" t="n">
-        <v>0.5233422256097561</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1.064405487804878</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0.820360137195122</v>
+      <c r="W15" t="n">
+        <v>3.779761904761905</v>
+      </c>
+      <c r="X15" t="n">
+        <v>10.21763392857143</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>6.300223214285714</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.772693452380952</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>3.121279761904762</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>2.329241071428572</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>Primary_min_mm</t>
+        </is>
+      </c>
+      <c r="AK15" s="2" t="n">
+        <v>13.65712691326531</v>
       </c>
     </row>
     <row r="16">
@@ -1124,35 +1814,82 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>8.214158239143368</v>
+        <v>3131.065759637188</v>
       </c>
       <c r="D16" t="n">
-        <v>20.46567041408725</v>
+        <v>399.5678509417034</v>
       </c>
       <c r="E16" t="n">
-        <v>13.32579089664831</v>
+        <v>260.1702032202766</v>
       </c>
       <c r="F16" t="n">
-        <v>1.535794053262141</v>
+        <v>1.53579405326214</v>
       </c>
       <c r="G16" t="n">
         <v>0.2464455481147751</v>
       </c>
       <c r="H16" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5190548780487805</v>
+        <v>1.489955357142857</v>
       </c>
       <c r="J16" t="n">
-        <v>1.054592225609756</v>
+        <v>20.58965773809524</v>
       </c>
       <c r="K16" t="n">
-        <v>0.818430830792683</v>
+        <v>7.356770833333333</v>
+      </c>
+      <c r="L16" t="n">
+        <v>3</v>
+      </c>
+      <c r="M16" t="n">
+        <v>20.58965773809524</v>
+      </c>
+      <c r="N16" t="n">
+        <v>16.79873511904762</v>
+      </c>
+      <c r="O16" t="n">
+        <v>16.39322916666666</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3</v>
+      </c>
+      <c r="T16" t="n">
+        <v>10.13392857142857</v>
+      </c>
+      <c r="U16" t="n">
+        <v>5.997023809523809</v>
+      </c>
+      <c r="V16" t="n">
+        <v>3.913690476190476</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.489955357142857</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>3.14360119047619</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.409164186507937</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>Primary_max_mm</t>
+        </is>
+      </c>
+      <c r="AK16" s="2" t="n">
+        <v>20.7085724914966</v>
       </c>
     </row>
     <row r="17">
@@ -1163,17 +1900,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>8.217430101130279</v>
+        <v>3132.312925170068</v>
       </c>
       <c r="D17" t="n">
-        <v>20.5371077962038</v>
+        <v>400.9625807830265</v>
       </c>
       <c r="E17" t="n">
-        <v>13.31742149155314</v>
+        <v>260.0068005493709</v>
       </c>
       <c r="F17" t="n">
         <v>1.542123436524848</v>
@@ -1182,16 +1919,60 @@
         <v>0.2448315134896502</v>
       </c>
       <c r="H17" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5359184451219512</v>
+        <v>1.473214285714286</v>
       </c>
       <c r="J17" t="n">
-        <v>1.049352134146341</v>
+        <v>20.48735119047619</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8287919207317074</v>
+        <v>7.601799242424243</v>
+      </c>
+      <c r="L17" t="n">
+        <v>3</v>
+      </c>
+      <c r="M17" t="n">
+        <v>20.48735119047619</v>
+      </c>
+      <c r="N17" t="n">
+        <v>17.20424107142857</v>
+      </c>
+      <c r="O17" t="n">
+        <v>16.56994047619047</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>10.46316964285714</v>
+      </c>
+      <c r="U17" t="n">
+        <v>3.926711309523809</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.473214285714286</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>3.089657738095238</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.494729662698413</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>Primary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AK17" s="2" t="n">
+        <v>16.55804900085034</v>
       </c>
     </row>
     <row r="18">
@@ -1202,35 +1983,73 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>8.157941701368234</v>
+        <v>3109.637188208616</v>
       </c>
       <c r="D18" t="n">
-        <v>20.58098557809504</v>
+        <v>401.8192422389984</v>
       </c>
       <c r="E18" t="n">
-        <v>13.31742150318332</v>
+        <v>260.0068007764362</v>
       </c>
       <c r="F18" t="n">
         <v>1.54541820075121</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2420238274693708</v>
+        <v>0.2420238274693707</v>
       </c>
       <c r="H18" t="n">
+        <v>11</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.981026785714286</v>
+      </c>
+      <c r="J18" t="n">
+        <v>21.10491071428571</v>
+      </c>
+      <c r="K18" t="n">
+        <v>7.812838203463202</v>
+      </c>
+      <c r="L18" t="n">
         <v>4</v>
       </c>
-      <c r="I18" t="n">
-        <v>0.606421493902439</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1.080983231707317</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0.8501810213414636</v>
+      <c r="P18" t="n">
+        <v>11.83965773809524</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>21.10491071428571</v>
+      </c>
+      <c r="R18" t="n">
+        <v>16.59877232142857</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.981026785714286</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>3.381696428571428</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.792304421768708</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="AK18" s="2" t="n">
+        <v>3.3</v>
       </c>
     </row>
     <row r="19">
@@ -1241,17 +2060,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>8.081499107674004</v>
+        <v>3080.498866213152</v>
       </c>
       <c r="D19" t="n">
-        <v>21.22451673775184</v>
+        <v>414.3834220227741</v>
       </c>
       <c r="E19" t="n">
-        <v>13.28884651893523</v>
+        <v>259.4489082268306</v>
       </c>
       <c r="F19" t="n">
         <v>1.597167723136023</v>
@@ -1260,16 +2079,57 @@
         <v>0.2254375065245756</v>
       </c>
       <c r="H19" t="n">
+        <v>11</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.016369047619047</v>
+      </c>
+      <c r="J19" t="n">
+        <v>21.06026785714286</v>
+      </c>
+      <c r="K19" t="n">
+        <v>8.045691287878787</v>
+      </c>
+      <c r="L19" t="n">
         <v>4</v>
       </c>
-      <c r="I19" t="n">
-        <v>0.6313833841463414</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1.078696646341464</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0.8660680259146342</v>
+      <c r="P19" t="n">
+        <v>12.32700892857143</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>21.06026785714286</v>
+      </c>
+      <c r="R19" t="n">
+        <v>16.90894717261905</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>4.293154761904762</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>2.016369047619047</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>3.350074404761905</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>2.762276785714286</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AK19" s="2" t="n">
+        <v>8.18369708994709</v>
       </c>
     </row>
     <row r="20">
@@ -1280,35 +2140,76 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>7.954491374182035</v>
+        <v>3032.086167800453</v>
       </c>
       <c r="D20" t="n">
-        <v>21.05205164595348</v>
+        <v>411.0162464209965</v>
       </c>
       <c r="E20" t="n">
-        <v>13.25435350871668</v>
+        <v>258.7754732654208</v>
       </c>
       <c r="F20" t="n">
         <v>1.588312219989355</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2255451151981393</v>
+        <v>0.2255451151981394</v>
       </c>
       <c r="H20" t="n">
+        <v>11</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.703869047619047</v>
+      </c>
+      <c r="J20" t="n">
+        <v>20.69754464285714</v>
+      </c>
+      <c r="K20" t="n">
+        <v>7.909057088744589</v>
+      </c>
+      <c r="L20" t="n">
         <v>4</v>
       </c>
-      <c r="I20" t="n">
-        <v>0.6290015243902439</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1.060118140243902</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0.8610899390243902</v>
+      <c r="P20" t="n">
+        <v>12.28050595238095</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>20.69754464285714</v>
+      </c>
+      <c r="R20" t="n">
+        <v>16.81175595238095</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.869047619047619</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.703869047619047</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>3.482142857142857</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>2.647259424603174</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AK20" s="2" t="n">
+        <v>5.820046768707483</v>
       </c>
     </row>
     <row r="21">
@@ -1319,17 +2220,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>7.746876859012493</v>
+        <v>2952.947845804988</v>
       </c>
       <c r="D21" t="n">
-        <v>22.51749703070013</v>
+        <v>439.6273229803357</v>
       </c>
       <c r="E21" t="n">
-        <v>13.25435352906948</v>
+        <v>258.7754736627851</v>
       </c>
       <c r="F21" t="n">
         <v>1.698875541633524</v>
@@ -1338,16 +2239,60 @@
         <v>0.1919978159194012</v>
       </c>
       <c r="H21" t="n">
+        <v>11</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.147693452380952</v>
+      </c>
+      <c r="J21" t="n">
+        <v>20.62127976190476</v>
+      </c>
+      <c r="K21" t="n">
+        <v>8.686755952380951</v>
+      </c>
+      <c r="L21" t="n">
         <v>4</v>
       </c>
-      <c r="I21" t="n">
-        <v>0.7384717987804879</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1.056211890243902</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0.8864567454268293</v>
+      <c r="P21" t="n">
+        <v>14.41778273809524</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>20.62127976190476</v>
+      </c>
+      <c r="R21" t="n">
+        <v>17.30701264880952</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2</v>
+      </c>
+      <c r="T21" t="n">
+        <v>7.898065476190475</v>
+      </c>
+      <c r="U21" t="n">
+        <v>6.497395833333333</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.147693452380952</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>3.288690476190476</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.386160714285714</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>Secondary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AK21" s="2" t="n">
+        <v>4.745163690476191</v>
       </c>
     </row>
     <row r="22">
@@ -1357,7 +2302,15 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.02439024390243903</v>
+        <v>0.4761904761904762</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>Secondary_min_mm</t>
+        </is>
+      </c>
+      <c r="AK22" s="2" t="n">
+        <v>4.276227678571429</v>
       </c>
     </row>
     <row r="23">
@@ -1371,6 +2324,14 @@
           <t>mm</t>
         </is>
       </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>Secondary_max_mm</t>
+        </is>
+      </c>
+      <c r="AK23" s="2" t="n">
+        <v>9.397135416666666</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1380,6 +2341,120 @@
       </c>
       <c r="B24" t="n">
         <v>25</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>Secondary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AK24" s="2" t="n">
+        <v>6.553084697420634</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ScalebarMeasuredPixels:</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="AK25" s="2" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldLength:</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>20</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>Tertiary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AK26" s="2" t="n">
+        <v>3.023933531746032</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldUnit:</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>Tertiary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AK27" s="2" t="n">
+        <v>2.692708333333333</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>Tertiary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AK28" s="2" t="n">
+        <v>1.977306547619047</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>Tertiary_min_mm</t>
+        </is>
+      </c>
+      <c r="AK29" s="2" t="n">
+        <v>1.704267644557823</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>Tertiary_max_mm</t>
+        </is>
+      </c>
+      <c r="AK30" s="2" t="n">
+        <v>3.239397321428572</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>Tertiary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AK31" s="2" t="n">
+        <v>2.519091844327016</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="AK32" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/measurements/35/Filled_2D_sections/coronal/week35_coronal_Batch_Allmarks.xlsx
+++ b/measurements/35/Filled_2D_sections/coronal/week35_coronal_Batch_Allmarks.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Analysis" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -137,6 +138,211 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>67</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>35</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5905500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2460,4 +2666,1277 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Workbook Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Workbook</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>week35_coronal_Batch_Allmarks.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Axis</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>coronal</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Slice rows analyzed</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>When a sulcus class count exceeds 3, approximate raw sulcus values are reconstructed from count + min/max/mean for summary stats and boxplots.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Core Metric Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>20</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3121.530612244897</v>
+      </c>
+      <c r="D10" t="n">
+        <v>70.49064241516083</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2952.947845804988</v>
+      </c>
+      <c r="F10" t="n">
+        <v>3231.519274376417</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>perimeter</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C11" t="n">
+        <v>432.6114635694595</v>
+      </c>
+      <c r="D11" t="n">
+        <v>25.89004224020521</v>
+      </c>
+      <c r="E11" t="n">
+        <v>399.5678509417034</v>
+      </c>
+      <c r="F11" t="n">
+        <v>477.3000356129238</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LGI</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>20</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.65576733231908</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.09886643973909784</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.526392625652185</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.823175299182073</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Compactness</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>20</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.2116000345760325</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.02432550773918939</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.1658249888635351</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.2464455481147751</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Counts Per Slice</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Sulci_count</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>band_axis1_s00_idx0141.png</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>11</v>
+      </c>
+      <c r="C17" t="n">
+        <v>4</v>
+      </c>
+      <c r="D17" t="n">
+        <v>6</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>11</v>
+      </c>
+      <c r="H17" t="n">
+        <v>4</v>
+      </c>
+      <c r="I17" t="n">
+        <v>6</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>band_axis1_s01_idx0143.png</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>12</v>
+      </c>
+      <c r="C18" t="n">
+        <v>4</v>
+      </c>
+      <c r="D18" t="n">
+        <v>5</v>
+      </c>
+      <c r="E18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>12</v>
+      </c>
+      <c r="H18" t="n">
+        <v>4</v>
+      </c>
+      <c r="I18" t="n">
+        <v>5</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>band_axis1_s02_idx0144.png</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>12</v>
+      </c>
+      <c r="C19" t="n">
+        <v>4</v>
+      </c>
+      <c r="D19" t="n">
+        <v>4</v>
+      </c>
+      <c r="E19" t="n">
+        <v>4</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>12</v>
+      </c>
+      <c r="H19" t="n">
+        <v>4</v>
+      </c>
+      <c r="I19" t="n">
+        <v>4</v>
+      </c>
+      <c r="J19" t="n">
+        <v>4</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>band_axis1_s03_idx0145.png</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>12</v>
+      </c>
+      <c r="C20" t="n">
+        <v>4</v>
+      </c>
+      <c r="D20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>12</v>
+      </c>
+      <c r="H20" t="n">
+        <v>4</v>
+      </c>
+      <c r="I20" t="n">
+        <v>4</v>
+      </c>
+      <c r="J20" t="n">
+        <v>4</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>band_axis1_s04_idx0146.png</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>13</v>
+      </c>
+      <c r="C21" t="n">
+        <v>4</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" t="n">
+        <v>6</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>13</v>
+      </c>
+      <c r="H21" t="n">
+        <v>4</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3</v>
+      </c>
+      <c r="J21" t="n">
+        <v>6</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>band_axis1_s05_idx0148.png</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>12</v>
+      </c>
+      <c r="C22" t="n">
+        <v>4</v>
+      </c>
+      <c r="D22" t="n">
+        <v>3</v>
+      </c>
+      <c r="E22" t="n">
+        <v>5</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>12</v>
+      </c>
+      <c r="H22" t="n">
+        <v>4</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3</v>
+      </c>
+      <c r="J22" t="n">
+        <v>5</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>band_axis1_s06_idx0149.png</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>12</v>
+      </c>
+      <c r="C23" t="n">
+        <v>4</v>
+      </c>
+      <c r="D23" t="n">
+        <v>4</v>
+      </c>
+      <c r="E23" t="n">
+        <v>4</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>12</v>
+      </c>
+      <c r="H23" t="n">
+        <v>4</v>
+      </c>
+      <c r="I23" t="n">
+        <v>4</v>
+      </c>
+      <c r="J23" t="n">
+        <v>4</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>band_axis1_s07_idx0150.png</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>11</v>
+      </c>
+      <c r="C24" t="n">
+        <v>4</v>
+      </c>
+      <c r="D24" t="n">
+        <v>4</v>
+      </c>
+      <c r="E24" t="n">
+        <v>3</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>11</v>
+      </c>
+      <c r="H24" t="n">
+        <v>4</v>
+      </c>
+      <c r="I24" t="n">
+        <v>4</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>band_axis1_s08_idx0151.png</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>10</v>
+      </c>
+      <c r="C25" t="n">
+        <v>4</v>
+      </c>
+      <c r="D25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>10</v>
+      </c>
+      <c r="H25" t="n">
+        <v>4</v>
+      </c>
+      <c r="I25" t="n">
+        <v>3</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>band_axis1_s09_idx0152.png</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>11</v>
+      </c>
+      <c r="C26" t="n">
+        <v>4</v>
+      </c>
+      <c r="D26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E26" t="n">
+        <v>3</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>11</v>
+      </c>
+      <c r="H26" t="n">
+        <v>4</v>
+      </c>
+      <c r="I26" t="n">
+        <v>4</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>band_axis1_s10_idx0154.png</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>12</v>
+      </c>
+      <c r="C27" t="n">
+        <v>3</v>
+      </c>
+      <c r="D27" t="n">
+        <v>6</v>
+      </c>
+      <c r="E27" t="n">
+        <v>3</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>12</v>
+      </c>
+      <c r="H27" t="n">
+        <v>3</v>
+      </c>
+      <c r="I27" t="n">
+        <v>6</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>band_axis1_s11_idx0155.png</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>11</v>
+      </c>
+      <c r="C28" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" t="n">
+        <v>4</v>
+      </c>
+      <c r="E28" t="n">
+        <v>4</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>11</v>
+      </c>
+      <c r="H28" t="n">
+        <v>3</v>
+      </c>
+      <c r="I28" t="n">
+        <v>4</v>
+      </c>
+      <c r="J28" t="n">
+        <v>4</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>band_axis1_s12_idx0156.png</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>12</v>
+      </c>
+      <c r="C29" t="n">
+        <v>3</v>
+      </c>
+      <c r="D29" t="n">
+        <v>3</v>
+      </c>
+      <c r="E29" t="n">
+        <v>6</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>12</v>
+      </c>
+      <c r="H29" t="n">
+        <v>3</v>
+      </c>
+      <c r="I29" t="n">
+        <v>3</v>
+      </c>
+      <c r="J29" t="n">
+        <v>6</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>band_axis1_s13_idx0157.png</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>12</v>
+      </c>
+      <c r="C30" t="n">
+        <v>3</v>
+      </c>
+      <c r="D30" t="n">
+        <v>4</v>
+      </c>
+      <c r="E30" t="n">
+        <v>5</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>12</v>
+      </c>
+      <c r="H30" t="n">
+        <v>3</v>
+      </c>
+      <c r="I30" t="n">
+        <v>4</v>
+      </c>
+      <c r="J30" t="n">
+        <v>5</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>band_axis1_s14_idx0158.png</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>12</v>
+      </c>
+      <c r="C31" t="n">
+        <v>3</v>
+      </c>
+      <c r="D31" t="n">
+        <v>3</v>
+      </c>
+      <c r="E31" t="n">
+        <v>6</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>12</v>
+      </c>
+      <c r="H31" t="n">
+        <v>3</v>
+      </c>
+      <c r="I31" t="n">
+        <v>3</v>
+      </c>
+      <c r="J31" t="n">
+        <v>6</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>band_axis1_s15_idx0160.png</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>11</v>
+      </c>
+      <c r="C32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E32" t="n">
+        <v>6</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>11</v>
+      </c>
+      <c r="H32" t="n">
+        <v>3</v>
+      </c>
+      <c r="I32" t="n">
+        <v>2</v>
+      </c>
+      <c r="J32" t="n">
+        <v>6</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>band_axis1_s16_idx0161.png</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>11</v>
+      </c>
+      <c r="C33" t="n">
+        <v>4</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
+        <v>7</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>11</v>
+      </c>
+      <c r="H33" t="n">
+        <v>4</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>7</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>band_axis1_s17_idx0162.png</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>11</v>
+      </c>
+      <c r="C34" t="n">
+        <v>4</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" t="n">
+        <v>6</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>11</v>
+      </c>
+      <c r="H34" t="n">
+        <v>4</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" t="n">
+        <v>6</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>band_axis1_s18_idx0163.png</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>11</v>
+      </c>
+      <c r="C35" t="n">
+        <v>4</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" t="n">
+        <v>6</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>11</v>
+      </c>
+      <c r="H35" t="n">
+        <v>4</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" t="n">
+        <v>6</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>band_axis1_s19_idx0164.png</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>11</v>
+      </c>
+      <c r="C36" t="n">
+        <v>4</v>
+      </c>
+      <c r="D36" t="n">
+        <v>2</v>
+      </c>
+      <c r="E36" t="n">
+        <v>5</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>11</v>
+      </c>
+      <c r="H36" t="n">
+        <v>4</v>
+      </c>
+      <c r="I36" t="n">
+        <v>2</v>
+      </c>
+      <c r="J36" t="n">
+        <v>5</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Count Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>20</v>
+      </c>
+      <c r="C40" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.6882472016116853</v>
+      </c>
+      <c r="E40" t="n">
+        <v>10</v>
+      </c>
+      <c r="F40" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>20</v>
+      </c>
+      <c r="C41" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.4701623459816273</v>
+      </c>
+      <c r="E41" t="n">
+        <v>3</v>
+      </c>
+      <c r="F41" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>20</v>
+      </c>
+      <c r="C42" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1.559352092174317</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>20</v>
+      </c>
+      <c r="C43" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1.538967528127731</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>20</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Sulcus Value Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>primary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>74</v>
+      </c>
+      <c r="C48" t="n">
+        <v>16.88123391248391</v>
+      </c>
+      <c r="D48" t="n">
+        <v>2.683057967609422</v>
+      </c>
+      <c r="E48" t="n">
+        <v>11.83965773809524</v>
+      </c>
+      <c r="F48" t="n">
+        <v>22.31212797619047</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>secondary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>66</v>
+      </c>
+      <c r="C49" t="n">
+        <v>6.547731782106782</v>
+      </c>
+      <c r="D49" t="n">
+        <v>2.18088104276325</v>
+      </c>
+      <c r="E49" t="n">
+        <v>3.779761904761905</v>
+      </c>
+      <c r="F49" t="n">
+        <v>10.84077380952381</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>tertiary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>90</v>
+      </c>
+      <c r="C50" t="n">
+        <v>2.542576058201058</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.5450208093843337</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1.147693452380952</v>
+      </c>
+      <c r="F50" t="n">
+        <v>3.809523809523809</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>unclassified_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>